--- a/sheets/대금율보/검수/사설시조 (여창).xlsx
+++ b/sheets/대금율보/검수/사설시조 (여창).xlsx
@@ -4119,8 +4119,7 @@
         <is>
           <t xml:space="preserve">汰∧⌇
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="C5" s="22"/>
@@ -4136,8 +4135,7 @@
         <is>
           <t xml:space="preserve">汰潢
 –И
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -4151,8 +4149,7 @@
         <is>
           <t xml:space="preserve">潢潢
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
@@ -4292,8 +4289,7 @@
         <is>
           <t xml:space="preserve">–И
 潢汰⌇
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="G7" s="22"/>
@@ -4310,7 +4306,7 @@
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林⌇
-–南‹
+–南
 ㅣ林И</t>
         </is>
       </c>
@@ -4325,8 +4321,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="Q7" s="22"/>
@@ -4499,8 +4494,7 @@
         <is>
           <t xml:space="preserve">潢潢
 –И
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -4512,15 +4506,13 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="G10" s="22"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌇
-‹</t>
+          <t xml:space="preserve">⌇</t>
         </is>
       </c>
       <c r="I10" s="22"/>
@@ -4540,8 +4532,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="M10" s="22"/>
@@ -4555,8 +4546,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="Q10" s="22"/>
@@ -4666,8 +4656,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4699,8 +4688,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -4716,11 +4704,7 @@
           <t xml:space="preserve">ㅁ</t>
         </is>
       </c>
-      <c r="P12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P12" s="21"/>
       <c r="Q12" s="22"/>
       <c r="R12" s="21"/>
       <c r="S12" s="22"/>
@@ -4866,8 +4850,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="O14" s="22"/>

--- a/sheets/대금율보/검수/사설시조 (여창).xlsx
+++ b/sheets/대금율보/검수/사설시조 (여창).xlsx
@@ -3905,30 +3905,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16.2" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.2" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="16.2" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="16.2" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="16.2" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="16.2" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.2" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="16.2" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="16.2" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="95.24" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="131.1" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="131.1" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="131.1" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="S5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="131.1" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="131.1" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="131.1" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="131.1" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4486,7 +4486,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="131.1" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -4553,7 +4553,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="131.1" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4636,7 +4636,7 @@
       <c r="R11" s="21"/>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="131.1" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4709,7 +4709,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="131.1" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -4794,7 +4794,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="131.1" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -4859,7 +4859,7 @@
       <c r="R14" s="21"/>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="131.1" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4944,6 +4944,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="42"/>
 </worksheet>
 </file>